--- a/doc/_static/example-files/PMHC-5-0-intake.xlsx
+++ b/doc/_static/example-files/PMHC-5-0-intake.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jennib/Work/git/PMHC/spec/doc/_static/example-files/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97AB4A0-46AF-7E4D-915B-9D536D633C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="27100" windowHeight="16720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -13,12 +19,12 @@
     <sheet name="Intakes" sheetId="4" r:id="rId4"/>
     <sheet name="IAR-DST" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="106">
   <si>
     <t>key</t>
   </si>
@@ -333,13 +339,16 @@
   </si>
   <si>
     <t>2.child</t>
+  </si>
+  <si>
+    <t>veteran</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,13 +385,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -420,7 +437,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -454,6 +471,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -488,9 +506,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -663,11 +682,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -675,7 +694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -683,7 +702,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -697,11 +716,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -736,7 +755,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -762,7 +781,7 @@
         <v>9099999</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -794,11 +813,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -833,7 +852,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -865,7 +884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -897,7 +916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -929,7 +948,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -961,7 +980,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -993,7 +1012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1031,11 +1050,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:O12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1067,19 +1086,22 @@
         <v>50</v>
       </c>
       <c r="K1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L1" t="s">
         <v>51</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>52</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>53</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1111,16 +1133,19 @@
         <v>9</v>
       </c>
       <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
         <v>30072021</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>56</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1152,16 +1177,19 @@
         <v>1</v>
       </c>
       <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
         <v>25062021</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>21</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1193,16 +1221,19 @@
         <v>1</v>
       </c>
       <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>4092021</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>59</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1234,16 +1265,19 @@
         <v>1</v>
       </c>
       <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
         <v>5082021</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>61</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1275,16 +1309,19 @@
         <v>9</v>
       </c>
       <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
         <v>1092021</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>63</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1316,16 +1353,19 @@
         <v>2</v>
       </c>
       <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
         <v>18082021</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>65</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1357,16 +1397,19 @@
         <v>2</v>
       </c>
       <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
         <v>5092021</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>67</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1398,16 +1441,19 @@
         <v>2</v>
       </c>
       <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
         <v>21022021</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>69</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1439,16 +1485,19 @@
         <v>9</v>
       </c>
       <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
         <v>12102021</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>71</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1480,16 +1529,19 @@
         <v>9</v>
       </c>
       <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11">
         <v>12052021</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>73</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1519,6 +1571,9 @@
       </c>
       <c r="J12">
         <v>2</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1527,11 +1582,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1581,7 +1636,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1628,7 +1683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1675,7 +1730,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1722,7 +1777,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1769,7 +1824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1816,7 +1871,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1863,7 +1918,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1910,7 +1965,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1957,7 +2012,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -2004,7 +2059,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -2051,7 +2106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
